--- a/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EHDS Data Category ValueSet (Final Regulation 2025/327)</t>
+    <t>EHDS Data Category ValueSet</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mandatory categories of electronic health data for secondary use according to Art. 51 EHDS.</t>
+    <t>Categories of electronic health data relevant for secondary-use documentation under the EHDS (EHDS Art. 51).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Property</t>
   </si>
@@ -36,13 +36,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>EHDS_DataCategoryVS</t>
+    <t>EHDSDataCategoryVS</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>EHDS Data Category ValueSet</t>
+    <t>EHDS Data Category Value Set</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:04:51+00:00</t>
+    <t>2026-07-31T11:07:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Categories of electronic health data relevant for secondary-use documentation under the EHDS (EHDS Art. 51).</t>
+    <t>Categories of electronic health data that may be documented for secondary-use and AI-development contexts.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -93,64 +93,16 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Concept</t>
-  </si>
-  <si>
-    <t>ehr</t>
-  </si>
-  <si>
-    <t>health-factors</t>
-  </si>
-  <si>
-    <t>healthcare-resources</t>
-  </si>
-  <si>
-    <t>pathogen-data</t>
-  </si>
-  <si>
-    <t>admin-claims</t>
-  </si>
-  <si>
-    <t>human-genomic</t>
-  </si>
-  <si>
-    <t>molecular-omics</t>
-  </si>
-  <si>
-    <t>device-generated-personal</t>
-  </si>
-  <si>
-    <t>wellness-apps</t>
-  </si>
-  <si>
-    <t>professional-status</t>
-  </si>
-  <si>
-    <t>public-health-registry</t>
-  </si>
-  <si>
-    <t>medical-mortality-registry</t>
-  </si>
-  <si>
-    <t>clinical-trial</t>
-  </si>
-  <si>
-    <t>medical-device-other</t>
-  </si>
-  <si>
-    <t>medicinal-device-registry</t>
-  </si>
-  <si>
-    <t>research-cohort-survey</t>
-  </si>
-  <si>
-    <t>biobank</t>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
   </si>
   <si>
     <t>System URI</t>
   </si>
   <si>
-    <t>http://example.org/fhir/eu-ai-transparency/CodeSystem/EUAIActCodeSystem</t>
+    <t>http://example.org/fhir/eu-ai-transparency/CodeSystem/ehds-data-category-cs</t>
   </si>
 </sst>
 </file>
@@ -406,7 +358,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -417,126 +369,26 @@
       <c r="A1" t="s" s="1">
         <v>26</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>20</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>27</v>
       </c>
-      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B3" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>19</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T11:07:29+00:00</t>
+    <t>2026-09-02T10:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:48:14+00:00</t>
+    <t>2026-09-03T11:53:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
+++ b/r5-aist-trustworthyai-main/ValueSet-ehds-data-category-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:53:05+00:00</t>
+    <t>2026-09-07T08:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
